--- a/debug/judgements_intro/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/phi-4/metrics_default_vs_simple.xlsx
+++ b/debug/judgements_intro/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/phi-4/metrics_default_vs_simple.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.7553191489361702</v>
+        <v>0.6888888888888889</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.5704225352112676</v>
+        <v>0.5915492957746479</v>
       </c>
       <c r="D2">
-        <v>0.4621212121212121</v>
+        <v>0.4833333333333333</v>
       </c>
       <c r="E2">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F2">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="G2">
-        <v>10</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
